--- a/output-Excel/HomeLoanEMI.xlsx
+++ b/output-Excel/HomeLoanEMI.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="272">
   <si>
     <t>Year</t>
   </si>
@@ -658,6 +658,192 @@
   </si>
   <si>
     <t>2039</t>
+  </si>
+  <si>
+    <t>₹ 1,03,044</t>
+  </si>
+  <si>
+    <t>₹ 1,84,581</t>
+  </si>
+  <si>
+    <t>₹ 49,000</t>
+  </si>
+  <si>
+    <t>₹ 3,36,625</t>
+  </si>
+  <si>
+    <t>₹ 38,96,956</t>
+  </si>
+  <si>
+    <t>2.58%</t>
+  </si>
+  <si>
+    <t>₹ 1,63,841</t>
+  </si>
+  <si>
+    <t>₹ 2,67,597</t>
+  </si>
+  <si>
+    <t>₹ 37,33,115</t>
+  </si>
+  <si>
+    <t>6.67%</t>
+  </si>
+  <si>
+    <t>₹ 1,75,685</t>
+  </si>
+  <si>
+    <t>₹ 2,55,753</t>
+  </si>
+  <si>
+    <t>₹ 35,57,430</t>
+  </si>
+  <si>
+    <t>11.06%</t>
+  </si>
+  <si>
+    <t>₹ 1,88,385</t>
+  </si>
+  <si>
+    <t>₹ 2,43,052</t>
+  </si>
+  <si>
+    <t>₹ 33,69,045</t>
+  </si>
+  <si>
+    <t>15.77%</t>
+  </si>
+  <si>
+    <t>₹ 2,02,004</t>
+  </si>
+  <si>
+    <t>₹ 2,29,434</t>
+  </si>
+  <si>
+    <t>₹ 31,67,041</t>
+  </si>
+  <si>
+    <t>20.82%</t>
+  </si>
+  <si>
+    <t>₹ 2,16,607</t>
+  </si>
+  <si>
+    <t>₹ 2,14,831</t>
+  </si>
+  <si>
+    <t>₹ 29,50,435</t>
+  </si>
+  <si>
+    <t>26.24%</t>
+  </si>
+  <si>
+    <t>₹ 2,32,265</t>
+  </si>
+  <si>
+    <t>₹ 1,99,172</t>
+  </si>
+  <si>
+    <t>₹ 27,18,169</t>
+  </si>
+  <si>
+    <t>32.05%</t>
+  </si>
+  <si>
+    <t>₹ 2,49,056</t>
+  </si>
+  <si>
+    <t>₹ 1,82,382</t>
+  </si>
+  <si>
+    <t>₹ 24,69,114</t>
+  </si>
+  <si>
+    <t>38.27%</t>
+  </si>
+  <si>
+    <t>₹ 2,67,060</t>
+  </si>
+  <si>
+    <t>₹ 1,64,378</t>
+  </si>
+  <si>
+    <t>₹ 22,02,054</t>
+  </si>
+  <si>
+    <t>44.95%</t>
+  </si>
+  <si>
+    <t>₹ 2,86,366</t>
+  </si>
+  <si>
+    <t>₹ 1,45,072</t>
+  </si>
+  <si>
+    <t>₹ 19,15,689</t>
+  </si>
+  <si>
+    <t>52.11%</t>
+  </si>
+  <si>
+    <t>₹ 3,07,067</t>
+  </si>
+  <si>
+    <t>₹ 1,24,371</t>
+  </si>
+  <si>
+    <t>₹ 16,08,622</t>
+  </si>
+  <si>
+    <t>59.78%</t>
+  </si>
+  <si>
+    <t>₹ 3,29,265</t>
+  </si>
+  <si>
+    <t>₹ 1,02,173</t>
+  </si>
+  <si>
+    <t>₹ 12,79,357</t>
+  </si>
+  <si>
+    <t>68.02%</t>
+  </si>
+  <si>
+    <t>₹ 3,53,067</t>
+  </si>
+  <si>
+    <t>₹ 78,370</t>
+  </si>
+  <si>
+    <t>₹ 9,26,289</t>
+  </si>
+  <si>
+    <t>76.84%</t>
+  </si>
+  <si>
+    <t>₹ 3,78,591</t>
+  </si>
+  <si>
+    <t>₹ 52,847</t>
+  </si>
+  <si>
+    <t>₹ 5,47,699</t>
+  </si>
+  <si>
+    <t>86.31%</t>
+  </si>
+  <si>
+    <t>₹ 4,05,959</t>
+  </si>
+  <si>
+    <t>₹ 25,479</t>
+  </si>
+  <si>
+    <t>₹ 1,41,739</t>
+  </si>
+  <si>
+    <t>96.46%</t>
   </si>
 </sst>
 </file>
@@ -1016,22 +1202,22 @@
         <v>26</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>10</v>
+        <v>212</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>11</v>
+        <v>213</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>12</v>
+        <v>214</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>13</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5">
@@ -1039,10 +1225,10 @@
         <v>31</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>15</v>
+        <v>216</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>16</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>17</v>
@@ -1051,10 +1237,10 @@
         <v>18</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>20</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7">
@@ -1062,10 +1248,10 @@
         <v>36</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>22</v>
+        <v>220</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>23</v>
+        <v>221</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>17</v>
@@ -1074,10 +1260,10 @@
         <v>18</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>24</v>
+        <v>222</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>25</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9">
@@ -1085,10 +1271,10 @@
         <v>41</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>27</v>
+        <v>224</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>28</v>
+        <v>225</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>17</v>
@@ -1097,10 +1283,10 @@
         <v>18</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>29</v>
+        <v>226</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>30</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1108,10 +1294,10 @@
         <v>46</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>17</v>
@@ -1120,10 +1306,10 @@
         <v>18</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>34</v>
+        <v>230</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>35</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13">
@@ -1131,10 +1317,10 @@
         <v>51</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>37</v>
+        <v>232</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>38</v>
+        <v>233</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>17</v>
@@ -1143,10 +1329,10 @@
         <v>18</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>39</v>
+        <v>234</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>40</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15">
@@ -1154,10 +1340,10 @@
         <v>56</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>42</v>
+        <v>236</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>43</v>
+        <v>237</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>17</v>
@@ -1166,10 +1352,10 @@
         <v>18</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>44</v>
+        <v>238</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>45</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17">
@@ -1177,10 +1363,10 @@
         <v>61</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>47</v>
+        <v>240</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>48</v>
+        <v>241</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>17</v>
@@ -1189,10 +1375,10 @@
         <v>18</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>49</v>
+        <v>242</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>50</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19">
@@ -1200,10 +1386,10 @@
         <v>66</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>52</v>
+        <v>244</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>53</v>
+        <v>245</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>17</v>
@@ -1212,10 +1398,10 @@
         <v>18</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>54</v>
+        <v>246</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>55</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21">
@@ -1223,10 +1409,10 @@
         <v>71</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>57</v>
+        <v>248</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>58</v>
+        <v>249</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>17</v>
@@ -1235,10 +1421,10 @@
         <v>18</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>59</v>
+        <v>250</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>60</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23">
@@ -1246,10 +1432,10 @@
         <v>76</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>62</v>
+        <v>252</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>63</v>
+        <v>253</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>17</v>
@@ -1258,10 +1444,10 @@
         <v>18</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>64</v>
+        <v>254</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>65</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25">
@@ -1269,10 +1455,10 @@
         <v>81</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>67</v>
+        <v>256</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>68</v>
+        <v>257</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>17</v>
@@ -1281,10 +1467,10 @@
         <v>18</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>69</v>
+        <v>258</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>70</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27">
@@ -1292,10 +1478,10 @@
         <v>142</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>73</v>
+        <v>261</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>17</v>
@@ -1304,10 +1490,10 @@
         <v>18</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>75</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29">
@@ -1315,10 +1501,10 @@
         <v>208</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>77</v>
+        <v>264</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>17</v>
@@ -1327,10 +1513,10 @@
         <v>18</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>80</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31">
@@ -1338,10 +1524,10 @@
         <v>209</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>83</v>
+        <v>269</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>17</v>
@@ -1350,10 +1536,10 @@
         <v>18</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>84</v>
+        <v>270</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>85</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
